--- a/outputs/gym-import-20261007/Gym_Member_Import_Template.xlsx
+++ b/outputs/gym-import-20261007/Gym_Member_Import_Template.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="1" r:id="R9bd80ee79faf456a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plans" sheetId="2" r:id="R0a41510ae2f3433e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R4b09db825d904625"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Members" sheetId="1" r:id="Ra6e53fa4487f4b12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plans" sheetId="2" r:id="R523d798cbcf04539"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R5fbfc91fd62a4e07"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4716,7 +4716,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7207ea19f68465a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6a660f6d42e4557"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5285,7 +5285,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc13d707bdbd04706"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2963712ed794d70"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5556,7 +5556,7 @@
         <x:v>Text starting with +; India is +91.</x:v>
       </x:c>
       <x:c r="D25" s="15" t="str">
-        <x:v>+91</x:v>
+        <x:v>'+91</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="43" customHeight="1">
